--- a/Tests/TestsDescription.xlsx
+++ b/Tests/TestsDescription.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FTISoftware\github_SandBox_PlayGround_pormisamigos\Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285FCA3D-04C4-44C6-AD73-D66A96B5B303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD99029-0905-4678-BA65-C8EE87F991A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="36">
   <si>
     <t>Test Name</t>
   </si>
@@ -120,22 +120,19 @@
     <t>UPS_Model_MIL</t>
   </si>
   <si>
-    <t>This is the first commit</t>
-  </si>
-  <si>
-    <t>0.0.0.0.0.0</t>
-  </si>
-  <si>
     <t>for testing automation gui</t>
   </si>
   <si>
-    <t>test_00000000_lalalal</t>
-  </si>
-  <si>
     <t>eyeball_of_the_fiercest</t>
   </si>
   <si>
     <t>no_model, nunca_model, net_momdeli</t>
+  </si>
+  <si>
+    <t>2nd commit</t>
+  </si>
+  <si>
+    <t>test1111111</t>
   </si>
 </sst>
 </file>
@@ -562,22 +559,22 @@
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="5">
+        <v>111111111</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="E2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="H2" s="5">
         <v>1</v>
